--- a/Tennis/step8_tennis_direction_clean.xlsx
+++ b/Tennis/step8_tennis_direction_clean.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS34"/>
+  <dimension ref="A1:AS37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Francis Marshall</t>
+          <t>Marcus Buchecha</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>FRANCIS MARSHALL</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -826,13 +826,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Fight Time (Mins)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>2.5</v>
+        <v>4.99</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.7669</v>
+        <v>0.8383</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2669</v>
+        <v>0.3383</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6015</v>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="inlineStr"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Ryan Spann</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -953,13 +953,13 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr"/>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -981,16 +981,16 @@
         <v>0</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.7669</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>0.2669</v>
+        <v>0.3372</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6012</v>
       </c>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Victor Valenzuela</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>VICTOR VALENZUELA</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1080,23 +1080,23 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:00 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Fight Time (Mins)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -1108,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.7644</v>
+        <v>0.8369</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.2644</v>
+        <v>0.3369</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5793</v>
+        <v>0.6011</v>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="inlineStr"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Michelle Montague</t>
+          <t>Montel Jackson</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>MICHELLE MONTAGUE</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1207,23 +1207,23 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -1235,16 +1235,16 @@
         <v>0</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>2.5</v>
+        <v>38.5</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.7644</v>
+        <v>0.8363</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>0.2644</v>
+        <v>0.3363</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.5793</v>
+        <v>0.6009</v>
       </c>
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="6" t="inlineStr"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Montel Jackson</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1365,13 +1365,13 @@
         <v>2.5</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7644</v>
+        <v>0.8357</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2644</v>
+        <v>0.3357</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5793</v>
+        <v>0.6007</v>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -1492,13 +1492,13 @@
         <v>2.5</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>0.7644</v>
+        <v>0.8357</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0.2644</v>
+        <v>0.3357</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.5793</v>
+        <v>0.6007</v>
       </c>
       <c r="T7" s="6" t="inlineStr"/>
       <c r="U7" s="6" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Francis Marshall</t>
+          <t>Joselyne Edwards</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>FRANCIS MARSHALL</t>
+          <t>JOSELYNE EDWARDS</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>NORMA VIANA</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1588,23 +1588,23 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 9:20 PM</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1.5</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8355</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3355</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.6007</v>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Jafel Filho</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>JAFEL FILHO</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CODY DURDEN</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1715,13 +1715,13 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
@@ -1743,16 +1743,16 @@
         <v>0</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.7524</v>
+        <v>0.8328</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>0.2524</v>
+        <v>0.3328</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.5757</v>
+        <v>0.5998</v>
       </c>
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1842,13 +1842,13 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -1870,16 +1870,16 @@
         <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8317</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3317</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.5995</v>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Victor Valenzuela</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>VICTOR VALENZUELA</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 5:00 PM</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -1997,16 +1997,16 @@
         <v>0</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>0.7524</v>
+        <v>0.8302</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0.2524</v>
+        <v>0.3302</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.5757</v>
+        <v>0.5991</v>
       </c>
       <c r="T11" s="6" t="inlineStr"/>
       <c r="U11" s="6" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Michelle Montague</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>MICHELLE MONTAGUE</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -2124,16 +2124,16 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8302</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3302</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.5991</v>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Montel Jackson</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr"/>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>0.7518</v>
+        <v>0.8302</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0.2518</v>
+        <v>0.3302</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.5755</v>
+        <v>0.5991</v>
       </c>
       <c r="T13" s="6" t="inlineStr"/>
       <c r="U13" s="6" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Davey Grant</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -2378,16 +2378,16 @@
         <v>0</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.7148</v>
+        <v>0.8302</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.2148</v>
+        <v>0.3302</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.5645</v>
+        <v>0.5991</v>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="inlineStr"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -2477,23 +2477,23 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Fight Time (Mins)</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -2505,16 +2505,16 @@
         <v>0</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.7034</v>
+        <v>0.8302</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>0.2034</v>
+        <v>0.3302</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5991</v>
       </c>
       <c r="T15" s="6" t="inlineStr"/>
       <c r="U15" s="6" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Raoni Barcelos</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -2604,13 +2604,13 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Fight Time (Mins)</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -2632,16 +2632,16 @@
         <v>0</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4.99</v>
+        <v>40.5</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.702</v>
+        <v>0.8292</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.202</v>
+        <v>0.3292</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.5606</v>
+        <v>0.5988</v>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="inlineStr"/>
@@ -2762,13 +2762,13 @@
         <v>12.5</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.5816</v>
+        <v>0.8288</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.3288</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.5245</v>
+        <v>0.5986</v>
       </c>
       <c r="T17" s="6" t="inlineStr"/>
       <c r="U17" s="6" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Juan Martinetti</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2858,23 +2858,23 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -2886,16 +2886,16 @@
         <v>0</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>1.5</v>
+        <v>65.5</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Cody Durden</t>
+          <t>Davey Grant</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>CODY DURDEN</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>JAFEL FILHO</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2985,23 +2985,23 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -3013,16 +3013,16 @@
         <v>0</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1.5</v>
+        <v>65.5</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T19" s="6" t="inlineStr"/>
       <c r="U19" s="6" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -3112,23 +3112,23 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -3140,16 +3140,16 @@
         <v>0</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.5</v>
+        <v>59.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="inlineStr"/>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Rafa Garcia</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -3239,23 +3239,23 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -3267,16 +3267,16 @@
         <v>0</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>1.5</v>
+        <v>54.5</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T21" s="6" t="inlineStr"/>
       <c r="U21" s="6" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Ryan Spann</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -3394,16 +3394,16 @@
         <v>0</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>15.5</v>
+        <v>59.5</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.5599</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.0599</v>
+        <v>0.3271</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.518</v>
+        <v>0.5981</v>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Aljamain Sterling</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -3493,23 +3493,23 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -3521,16 +3521,16 @@
         <v>0</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>2.5</v>
+        <v>53.5</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.4989</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>-0.0011</v>
+        <v>0.3271</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.4997</v>
+        <v>0.5981</v>
       </c>
       <c r="T23" s="6" t="inlineStr"/>
       <c r="U23" s="6" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Norma Viana</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>NORMA VIANA</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>JOSELYNE EDWARDS</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -3620,23 +3620,23 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:20 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -3648,16 +3648,16 @@
         <v>0</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>2.5</v>
+        <v>52.5</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.4989</v>
+        <v>0.8161</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>-0.0011</v>
+        <v>0.3161</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.4997</v>
+        <v>0.5948</v>
       </c>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="3" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Raoni Barcelos</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -3747,23 +3747,23 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>40.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.4255</v>
+        <v>0.7938</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>-0.0745</v>
+        <v>0.2938</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.4776</v>
+        <v>0.5881</v>
       </c>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Norma Viana</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>NORMA VIANA</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>JOSELYNE EDWARDS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -3874,23 +3874,23 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -3902,16 +3902,16 @@
         <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>52.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.417</v>
+        <v>0.7938</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.083</v>
+        <v>0.2938</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.4751</v>
+        <v>0.5881</v>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="3" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Aljamain Sterling</t>
+          <t>Jafel Filho</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>JAFEL FILHO</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>CODY DURDEN</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -4001,23 +4001,23 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -4029,16 +4029,16 @@
         <v>0</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>53.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.417</v>
+        <v>0.7938</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>-0.083</v>
+        <v>0.2938</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.4751</v>
+        <v>0.5881</v>
       </c>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Montel Jackson</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -4128,23 +4128,23 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>38.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.4115</v>
+        <v>0.7938</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>-0.0885</v>
+        <v>0.2938</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.4735</v>
+        <v>0.5881</v>
       </c>
       <c r="T28" s="3" t="inlineStr"/>
       <c r="U28" s="3" t="inlineStr"/>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Juan Martinetti</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>JUAN MARTINETTI</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>DAVEY GRANT</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -4255,23 +4255,23 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>04/25 8:40 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -4283,16 +4283,16 @@
         <v>0</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>65.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.7938</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.2938</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5881</v>
       </c>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Davey Grant</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>DAVEY GRANT</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>JUAN MARTINETTI</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -4382,23 +4382,23 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:40 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -4410,16 +4410,16 @@
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>65.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.4037</v>
+        <v>0.7938</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-0.0963</v>
+        <v>0.2938</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0.4711</v>
+        <v>0.5881</v>
       </c>
       <c r="T30" s="3" t="inlineStr"/>
       <c r="U30" s="3" t="inlineStr"/>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -4509,23 +4509,23 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -4537,16 +4537,16 @@
         <v>0</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>59.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.7689</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.2689</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5807</v>
       </c>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Rafa Garcia</t>
+          <t>Marcus Buchecha</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -4636,23 +4636,23 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
@@ -4664,16 +4664,16 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>54.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>0.4037</v>
+        <v>0.7689</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>-0.0963</v>
+        <v>0.2689</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>0.4711</v>
+        <v>0.5807</v>
       </c>
       <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="3" t="inlineStr"/>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -4763,23 +4763,23 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr"/>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -4791,16 +4791,16 @@
         <v>0</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>59.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.6861</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.1861</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5558</v>
       </c>
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Joselyne Edwards</t>
+          <t>Cody Durden</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>JOSELYNE EDWARDS</t>
+          <t>CODY DURDEN</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>NORMA VIANA</t>
+          <t>JAFEL FILHO</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -4890,23 +4890,23 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:20 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -4918,16 +4918,16 @@
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>39.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0.3532</v>
+        <v>0.6861</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>-0.1468</v>
+        <v>0.1861</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0.456</v>
+        <v>0.5558</v>
       </c>
       <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="3" t="inlineStr"/>
@@ -4976,6 +4976,387 @@
       </c>
       <c r="AS34" s="3" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Marcus Buchecha</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>MARCUS BUCHECHA</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>RYAN SPANN</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>04/25 8:00 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Total Rounds</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
+      <c r="Y35" s="6" t="inlineStr"/>
+      <c r="Z35" s="6" t="inlineStr"/>
+      <c r="AA35" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB35" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC35" s="6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD35" s="6" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE35" s="6" t="inlineStr"/>
+      <c r="AF35" s="6" t="inlineStr"/>
+      <c r="AG35" s="6" t="inlineStr"/>
+      <c r="AH35" s="6" t="inlineStr"/>
+      <c r="AI35" s="6" t="inlineStr"/>
+      <c r="AJ35" s="6" t="inlineStr"/>
+      <c r="AK35" s="6" t="inlineStr"/>
+      <c r="AL35" s="6" t="inlineStr"/>
+      <c r="AM35" s="6" t="inlineStr"/>
+      <c r="AN35" s="6" t="inlineStr"/>
+      <c r="AO35" s="6" t="inlineStr"/>
+      <c r="AP35" s="6" t="inlineStr"/>
+      <c r="AQ35" s="6" t="inlineStr"/>
+      <c r="AR35" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Marcus Buchecha</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>MARCUS BUCHECHA</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>RYAN SPANN</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>04/25 8:00 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Takedowns</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE36" s="3" t="inlineStr"/>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr"/>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr"/>
+      <c r="AM36" s="3" t="inlineStr"/>
+      <c r="AN36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Youssef Zalal</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>YOUSSEF ZALAL</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>ALJAMAIN STERLING</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>04/25 9:40 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Takedowns</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr"/>
+      <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
+      <c r="Y37" s="6" t="inlineStr"/>
+      <c r="Z37" s="6" t="inlineStr"/>
+      <c r="AA37" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB37" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC37" s="6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD37" s="6" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE37" s="6" t="inlineStr"/>
+      <c r="AF37" s="6" t="inlineStr"/>
+      <c r="AG37" s="6" t="inlineStr"/>
+      <c r="AH37" s="6" t="inlineStr"/>
+      <c r="AI37" s="6" t="inlineStr"/>
+      <c r="AJ37" s="6" t="inlineStr"/>
+      <c r="AK37" s="6" t="inlineStr"/>
+      <c r="AL37" s="6" t="inlineStr"/>
+      <c r="AM37" s="6" t="inlineStr"/>
+      <c r="AN37" s="6" t="inlineStr"/>
+      <c r="AO37" s="6" t="inlineStr"/>
+      <c r="AP37" s="6" t="inlineStr"/>
+      <c r="AQ37" s="6" t="inlineStr"/>
+      <c r="AR37" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS37" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AS1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4988,7 +5369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS34"/>
+  <dimension ref="A1:AS37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5276,7 +5657,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Francis Marshall</t>
+          <t>Marcus Buchecha</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -5291,12 +5672,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>FRANCIS MARSHALL</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -5306,13 +5687,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Fight Time (Mins)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5322,7 +5703,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
@@ -5334,16 +5715,16 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>2.5</v>
+        <v>4.99</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.7669</v>
+        <v>0.8383</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2669</v>
+        <v>0.3383</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6015</v>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="inlineStr"/>
@@ -5403,7 +5784,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Ryan Spann</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -5418,12 +5799,12 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -5433,13 +5814,13 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr"/>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -5449,7 +5830,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -5461,16 +5842,16 @@
         <v>0</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.7669</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>0.2669</v>
+        <v>0.3372</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6012</v>
       </c>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
@@ -5530,7 +5911,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Victor Valenzuela</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -5545,7 +5926,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>VICTOR VALENZUELA</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -5560,23 +5941,23 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:00 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Fight Time (Mins)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -5588,16 +5969,16 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.7644</v>
+        <v>0.8369</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.2644</v>
+        <v>0.3369</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5793</v>
+        <v>0.6011</v>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="inlineStr"/>
@@ -5657,7 +6038,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Michelle Montague</t>
+          <t>Montel Jackson</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -5672,12 +6053,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>MICHELLE MONTAGUE</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -5687,23 +6068,23 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -5715,16 +6096,16 @@
         <v>0</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>2.5</v>
+        <v>38.5</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.7644</v>
+        <v>0.8363</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>0.2644</v>
+        <v>0.3363</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.5793</v>
+        <v>0.6009</v>
       </c>
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="6" t="inlineStr"/>
@@ -5784,7 +6165,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Montel Jackson</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -5799,12 +6180,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -5814,7 +6195,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
@@ -5825,7 +6206,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -5845,13 +6226,13 @@
         <v>2.5</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7644</v>
+        <v>0.8357</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2644</v>
+        <v>0.3357</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5793</v>
+        <v>0.6007</v>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="inlineStr"/>
@@ -5911,7 +6292,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -5926,12 +6307,12 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -5941,7 +6322,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
@@ -5952,7 +6333,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -5972,13 +6353,13 @@
         <v>2.5</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>0.7644</v>
+        <v>0.8357</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0.2644</v>
+        <v>0.3357</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.5793</v>
+        <v>0.6007</v>
       </c>
       <c r="T7" s="6" t="inlineStr"/>
       <c r="U7" s="6" t="inlineStr"/>
@@ -6038,7 +6419,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Francis Marshall</t>
+          <t>Joselyne Edwards</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -6053,12 +6434,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>FRANCIS MARSHALL</t>
+          <t>JOSELYNE EDWARDS</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>NORMA VIANA</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -6068,23 +6449,23 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 9:20 PM</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -6096,16 +6477,16 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1.5</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8355</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3355</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.6007</v>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="inlineStr"/>
@@ -6165,7 +6546,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Jafel Filho</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -6180,12 +6561,12 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>JAFEL FILHO</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CODY DURDEN</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -6195,13 +6576,13 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -6211,7 +6592,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
@@ -6223,16 +6604,16 @@
         <v>0</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.7524</v>
+        <v>0.8328</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>0.2524</v>
+        <v>0.3328</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.5757</v>
+        <v>0.5998</v>
       </c>
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
@@ -6292,7 +6673,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -6307,12 +6688,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -6322,13 +6703,13 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6338,7 +6719,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -6350,16 +6731,16 @@
         <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8317</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3317</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.5995</v>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="inlineStr"/>
@@ -6419,7 +6800,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Victor Valenzuela</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -6434,7 +6815,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>VICTOR VALENZUELA</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -6449,7 +6830,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 5:00 PM</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr"/>
@@ -6465,7 +6846,7 @@
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -6477,16 +6858,16 @@
         <v>0</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>0.7524</v>
+        <v>0.8302</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0.2524</v>
+        <v>0.3302</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.5757</v>
+        <v>0.5991</v>
       </c>
       <c r="T11" s="6" t="inlineStr"/>
       <c r="U11" s="6" t="inlineStr"/>
@@ -6546,7 +6927,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Michelle Montague</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -6561,12 +6942,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>MICHELLE MONTAGUE</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -6576,7 +6957,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -6592,7 +6973,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -6604,16 +6985,16 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8302</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3302</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.5991</v>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="inlineStr"/>
@@ -6673,7 +7054,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Montel Jackson</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -6688,12 +7069,12 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -6703,7 +7084,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr"/>
@@ -6719,7 +7100,7 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
@@ -6731,16 +7112,16 @@
         <v>0</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>0.7518</v>
+        <v>0.8302</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0.2518</v>
+        <v>0.3302</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.5755</v>
+        <v>0.5991</v>
       </c>
       <c r="T13" s="6" t="inlineStr"/>
       <c r="U13" s="6" t="inlineStr"/>
@@ -6800,7 +7181,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Davey Grant</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -6815,12 +7196,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -6830,7 +7211,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -6846,7 +7227,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -6858,16 +7239,16 @@
         <v>0</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.7148</v>
+        <v>0.8302</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.2148</v>
+        <v>0.3302</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.5645</v>
+        <v>0.5991</v>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="inlineStr"/>
@@ -6927,7 +7308,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -6942,12 +7323,12 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -6957,23 +7338,23 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Fight Time (Mins)</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -6985,16 +7366,16 @@
         <v>0</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.7034</v>
+        <v>0.8302</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>0.2034</v>
+        <v>0.3302</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5991</v>
       </c>
       <c r="T15" s="6" t="inlineStr"/>
       <c r="U15" s="6" t="inlineStr"/>
@@ -7054,7 +7435,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Raoni Barcelos</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -7069,12 +7450,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -7084,13 +7465,13 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Fight Time (Mins)</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -7100,7 +7481,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -7112,16 +7493,16 @@
         <v>0</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4.99</v>
+        <v>40.5</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.702</v>
+        <v>0.8292</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.202</v>
+        <v>0.3292</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.5606</v>
+        <v>0.5988</v>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="inlineStr"/>
@@ -7242,13 +7623,13 @@
         <v>12.5</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.5816</v>
+        <v>0.8288</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.3288</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.5245</v>
+        <v>0.5986</v>
       </c>
       <c r="T17" s="6" t="inlineStr"/>
       <c r="U17" s="6" t="inlineStr"/>
@@ -7308,7 +7689,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Juan Martinetti</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -7323,12 +7704,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -7338,23 +7719,23 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -7366,16 +7747,16 @@
         <v>0</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>1.5</v>
+        <v>65.5</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="inlineStr"/>
@@ -7435,7 +7816,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Cody Durden</t>
+          <t>Davey Grant</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -7450,12 +7831,12 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>CODY DURDEN</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>JAFEL FILHO</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -7465,23 +7846,23 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -7493,16 +7874,16 @@
         <v>0</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1.5</v>
+        <v>65.5</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T19" s="6" t="inlineStr"/>
       <c r="U19" s="6" t="inlineStr"/>
@@ -7562,7 +7943,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -7577,12 +7958,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -7592,23 +7973,23 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -7620,16 +8001,16 @@
         <v>0</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.5</v>
+        <v>59.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="inlineStr"/>
@@ -7689,7 +8070,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Rafa Garcia</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -7704,12 +8085,12 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -7719,23 +8100,23 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -7747,16 +8128,16 @@
         <v>0</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>1.5</v>
+        <v>54.5</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T21" s="6" t="inlineStr"/>
       <c r="U21" s="6" t="inlineStr"/>
@@ -7816,7 +8197,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Ryan Spann</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -7831,12 +8212,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -7846,7 +8227,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -7862,7 +8243,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -7874,16 +8255,16 @@
         <v>0</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>15.5</v>
+        <v>59.5</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.5599</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.0599</v>
+        <v>0.3271</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.518</v>
+        <v>0.5981</v>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="inlineStr"/>
@@ -7943,7 +8324,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Aljamain Sterling</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -7958,12 +8339,12 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -7973,23 +8354,23 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -8001,16 +8382,16 @@
         <v>0</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>2.5</v>
+        <v>53.5</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.4989</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>-0.0011</v>
+        <v>0.3271</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.4997</v>
+        <v>0.5981</v>
       </c>
       <c r="T23" s="6" t="inlineStr"/>
       <c r="U23" s="6" t="inlineStr"/>
@@ -8070,7 +8451,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Norma Viana</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -8085,12 +8466,12 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>NORMA VIANA</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>JOSELYNE EDWARDS</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -8100,23 +8481,23 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:20 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -8128,16 +8509,16 @@
         <v>0</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>2.5</v>
+        <v>52.5</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.4989</v>
+        <v>0.8161</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>-0.0011</v>
+        <v>0.3161</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.4997</v>
+        <v>0.5948</v>
       </c>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="3" t="inlineStr"/>
@@ -8197,7 +8578,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Raoni Barcelos</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -8212,12 +8593,12 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -8227,23 +8608,23 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -8255,16 +8636,16 @@
         <v>0</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>40.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.4255</v>
+        <v>0.7938</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>-0.0745</v>
+        <v>0.2938</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.4776</v>
+        <v>0.5881</v>
       </c>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
@@ -8324,7 +8705,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Norma Viana</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -8339,12 +8720,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>NORMA VIANA</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>JOSELYNE EDWARDS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -8354,23 +8735,23 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -8382,16 +8763,16 @@
         <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>52.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.417</v>
+        <v>0.7938</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.083</v>
+        <v>0.2938</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.4751</v>
+        <v>0.5881</v>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="3" t="inlineStr"/>
@@ -8451,7 +8832,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Aljamain Sterling</t>
+          <t>Jafel Filho</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -8466,12 +8847,12 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>JAFEL FILHO</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>CODY DURDEN</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -8481,23 +8862,23 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -8509,16 +8890,16 @@
         <v>0</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>53.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.417</v>
+        <v>0.7938</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>-0.083</v>
+        <v>0.2938</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.4751</v>
+        <v>0.5881</v>
       </c>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
@@ -8578,7 +8959,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Montel Jackson</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -8593,12 +8974,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -8608,23 +8989,23 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -8636,16 +9017,16 @@
         <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>38.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.4115</v>
+        <v>0.7938</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>-0.0885</v>
+        <v>0.2938</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.4735</v>
+        <v>0.5881</v>
       </c>
       <c r="T28" s="3" t="inlineStr"/>
       <c r="U28" s="3" t="inlineStr"/>
@@ -8705,7 +9086,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Juan Martinetti</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -8720,12 +9101,12 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>JUAN MARTINETTI</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>DAVEY GRANT</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -8735,23 +9116,23 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>04/25 8:40 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -8763,16 +9144,16 @@
         <v>0</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>65.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.7938</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.2938</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5881</v>
       </c>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
@@ -8832,7 +9213,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Davey Grant</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -8847,12 +9228,12 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>DAVEY GRANT</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>JUAN MARTINETTI</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -8862,23 +9243,23 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:40 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -8890,16 +9271,16 @@
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>65.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.4037</v>
+        <v>0.7938</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-0.0963</v>
+        <v>0.2938</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0.4711</v>
+        <v>0.5881</v>
       </c>
       <c r="T30" s="3" t="inlineStr"/>
       <c r="U30" s="3" t="inlineStr"/>
@@ -8959,7 +9340,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -8974,12 +9355,12 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -8989,23 +9370,23 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -9017,16 +9398,16 @@
         <v>0</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>59.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.7689</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.2689</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5807</v>
       </c>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
@@ -9086,7 +9467,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Rafa Garcia</t>
+          <t>Marcus Buchecha</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -9101,12 +9482,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -9116,23 +9497,23 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
@@ -9144,16 +9525,16 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>54.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>0.4037</v>
+        <v>0.7689</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>-0.0963</v>
+        <v>0.2689</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>0.4711</v>
+        <v>0.5807</v>
       </c>
       <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="3" t="inlineStr"/>
@@ -9213,7 +9594,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -9228,12 +9609,12 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -9243,23 +9624,23 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr"/>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -9271,16 +9652,16 @@
         <v>0</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>59.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.6861</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.1861</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5558</v>
       </c>
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
@@ -9340,7 +9721,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Joselyne Edwards</t>
+          <t>Cody Durden</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -9355,12 +9736,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>JOSELYNE EDWARDS</t>
+          <t>CODY DURDEN</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>NORMA VIANA</t>
+          <t>JAFEL FILHO</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -9370,23 +9751,23 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:20 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -9398,16 +9779,16 @@
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>39.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0.3532</v>
+        <v>0.6861</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>-0.1468</v>
+        <v>0.1861</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0.456</v>
+        <v>0.5558</v>
       </c>
       <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="3" t="inlineStr"/>
@@ -9455,6 +9836,387 @@
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Marcus Buchecha</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>MARCUS BUCHECHA</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>RYAN SPANN</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>04/25 8:00 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Total Rounds</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
+      <c r="Y35" s="6" t="inlineStr"/>
+      <c r="Z35" s="6" t="inlineStr"/>
+      <c r="AA35" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB35" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC35" s="6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD35" s="6" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE35" s="6" t="inlineStr"/>
+      <c r="AF35" s="6" t="inlineStr"/>
+      <c r="AG35" s="6" t="inlineStr"/>
+      <c r="AH35" s="6" t="inlineStr"/>
+      <c r="AI35" s="6" t="inlineStr"/>
+      <c r="AJ35" s="6" t="inlineStr"/>
+      <c r="AK35" s="6" t="inlineStr"/>
+      <c r="AL35" s="6" t="inlineStr"/>
+      <c r="AM35" s="6" t="inlineStr"/>
+      <c r="AN35" s="6" t="inlineStr"/>
+      <c r="AO35" s="6" t="inlineStr"/>
+      <c r="AP35" s="6" t="inlineStr"/>
+      <c r="AQ35" s="6" t="inlineStr"/>
+      <c r="AR35" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Marcus Buchecha</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>MARCUS BUCHECHA</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>RYAN SPANN</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>04/25 8:00 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Takedowns</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE36" s="3" t="inlineStr"/>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr"/>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr"/>
+      <c r="AM36" s="3" t="inlineStr"/>
+      <c r="AN36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Youssef Zalal</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>YOUSSEF ZALAL</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>ALJAMAIN STERLING</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>04/25 9:40 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Takedowns</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr"/>
+      <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
+      <c r="Y37" s="6" t="inlineStr"/>
+      <c r="Z37" s="6" t="inlineStr"/>
+      <c r="AA37" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB37" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC37" s="6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD37" s="6" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE37" s="6" t="inlineStr"/>
+      <c r="AF37" s="6" t="inlineStr"/>
+      <c r="AG37" s="6" t="inlineStr"/>
+      <c r="AH37" s="6" t="inlineStr"/>
+      <c r="AI37" s="6" t="inlineStr"/>
+      <c r="AJ37" s="6" t="inlineStr"/>
+      <c r="AK37" s="6" t="inlineStr"/>
+      <c r="AL37" s="6" t="inlineStr"/>
+      <c r="AM37" s="6" t="inlineStr"/>
+      <c r="AN37" s="6" t="inlineStr"/>
+      <c r="AO37" s="6" t="inlineStr"/>
+      <c r="AP37" s="6" t="inlineStr"/>
+      <c r="AQ37" s="6" t="inlineStr"/>
+      <c r="AR37" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS37" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AS1"/>
@@ -9757,7 +10519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS34"/>
+  <dimension ref="A1:AS37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10045,7 +10807,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Francis Marshall</t>
+          <t>Marcus Buchecha</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -10060,12 +10822,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>FRANCIS MARSHALL</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -10075,13 +10837,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Fight Time (Mins)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -10091,7 +10853,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
@@ -10103,16 +10865,16 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>2.5</v>
+        <v>4.99</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.7669</v>
+        <v>0.8383</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2669</v>
+        <v>0.3383</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6015</v>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="inlineStr"/>
@@ -10172,7 +10934,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Ryan Spann</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -10187,12 +10949,12 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -10202,13 +10964,13 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr"/>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -10218,7 +10980,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -10230,16 +10992,16 @@
         <v>0</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.7669</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>0.2669</v>
+        <v>0.3372</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6012</v>
       </c>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
@@ -10299,7 +11061,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Victor Valenzuela</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -10314,7 +11076,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>VICTOR VALENZUELA</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -10329,23 +11091,23 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:00 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Fight Time (Mins)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -10357,16 +11119,16 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.7644</v>
+        <v>0.8369</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.2644</v>
+        <v>0.3369</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5793</v>
+        <v>0.6011</v>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="inlineStr"/>
@@ -10426,7 +11188,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Michelle Montague</t>
+          <t>Montel Jackson</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -10441,12 +11203,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>MICHELLE MONTAGUE</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -10456,23 +11218,23 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -10484,16 +11246,16 @@
         <v>0</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>2.5</v>
+        <v>38.5</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.7644</v>
+        <v>0.8363</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>0.2644</v>
+        <v>0.3363</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0.5793</v>
+        <v>0.6009</v>
       </c>
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="6" t="inlineStr"/>
@@ -10553,7 +11315,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Montel Jackson</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -10568,12 +11330,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -10583,7 +11345,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
@@ -10594,7 +11356,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -10614,13 +11376,13 @@
         <v>2.5</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7644</v>
+        <v>0.8357</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2644</v>
+        <v>0.3357</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5793</v>
+        <v>0.6007</v>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="inlineStr"/>
@@ -10680,7 +11442,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -10695,12 +11457,12 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -10710,7 +11472,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
@@ -10721,7 +11483,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -10741,13 +11503,13 @@
         <v>2.5</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>0.7644</v>
+        <v>0.8357</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0.2644</v>
+        <v>0.3357</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.5793</v>
+        <v>0.6007</v>
       </c>
       <c r="T7" s="6" t="inlineStr"/>
       <c r="U7" s="6" t="inlineStr"/>
@@ -10807,7 +11569,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Francis Marshall</t>
+          <t>Joselyne Edwards</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -10822,12 +11584,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>FRANCIS MARSHALL</t>
+          <t>JOSELYNE EDWARDS</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>NORMA VIANA</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -10837,23 +11599,23 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>04/25 5:40 PM</t>
+          <t>04/25 9:20 PM</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -10865,16 +11627,16 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1.5</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8355</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3355</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.6007</v>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="inlineStr"/>
@@ -10934,7 +11696,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Jafel Filho</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -10949,12 +11711,12 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>JAFEL FILHO</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CODY DURDEN</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -10964,13 +11726,13 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -10980,7 +11742,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
@@ -10992,16 +11754,16 @@
         <v>0</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.7524</v>
+        <v>0.8328</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>0.2524</v>
+        <v>0.3328</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0.5757</v>
+        <v>0.5998</v>
       </c>
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
@@ -11061,7 +11823,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -11076,12 +11838,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -11091,13 +11853,13 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -11107,7 +11869,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -11119,16 +11881,16 @@
         <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8317</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3317</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.5995</v>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="inlineStr"/>
@@ -11188,7 +11950,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Rodolfo Vieira</t>
+          <t>Victor Valenzuela</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -11203,7 +11965,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>RODOLFO VIEIRA</t>
+          <t>VICTOR VALENZUELA</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -11218,7 +11980,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:20 PM</t>
+          <t>04/25 5:00 PM</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr"/>
@@ -11234,7 +11996,7 @@
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -11246,16 +12008,16 @@
         <v>0</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>0.7524</v>
+        <v>0.8302</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0.2524</v>
+        <v>0.3302</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.5757</v>
+        <v>0.5991</v>
       </c>
       <c r="T11" s="6" t="inlineStr"/>
       <c r="U11" s="6" t="inlineStr"/>
@@ -11315,7 +12077,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Michelle Montague</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -11330,12 +12092,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>MICHELLE MONTAGUE</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -11345,7 +12107,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -11361,7 +12123,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -11373,16 +12135,16 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.7524</v>
+        <v>0.8302</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.2524</v>
+        <v>0.3302</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.5757</v>
+        <v>0.5991</v>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="inlineStr"/>
@@ -11442,7 +12204,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Montel Jackson</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -11457,12 +12219,12 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -11472,7 +12234,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr"/>
@@ -11488,7 +12250,7 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
@@ -11500,16 +12262,16 @@
         <v>0</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>0.7518</v>
+        <v>0.8302</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0.2518</v>
+        <v>0.3302</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.5755</v>
+        <v>0.5991</v>
       </c>
       <c r="T13" s="6" t="inlineStr"/>
       <c r="U13" s="6" t="inlineStr"/>
@@ -11569,7 +12331,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Davey Grant</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -11584,12 +12346,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -11599,7 +12361,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -11615,7 +12377,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -11627,16 +12389,16 @@
         <v>0</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.7148</v>
+        <v>0.8302</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.2148</v>
+        <v>0.3302</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.5645</v>
+        <v>0.5991</v>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="inlineStr"/>
@@ -11696,7 +12458,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -11711,12 +12473,12 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -11726,23 +12488,23 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Fight Time (Mins)</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -11754,16 +12516,16 @@
         <v>0</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.7034</v>
+        <v>0.8302</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>0.2034</v>
+        <v>0.3302</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5991</v>
       </c>
       <c r="T15" s="6" t="inlineStr"/>
       <c r="U15" s="6" t="inlineStr"/>
@@ -11823,7 +12585,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Raoni Barcelos</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -11838,12 +12600,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>RAONI BARCELOS</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>MONTEL JACKSON</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -11853,13 +12615,13 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 8:20 PM</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Fight Time (Mins)</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -11869,7 +12631,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -11881,16 +12643,16 @@
         <v>0</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4.99</v>
+        <v>40.5</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.702</v>
+        <v>0.8292</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.202</v>
+        <v>0.3292</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.5606</v>
+        <v>0.5988</v>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="inlineStr"/>
@@ -12011,13 +12773,13 @@
         <v>12.5</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.5816</v>
+        <v>0.8288</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.3288</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.5245</v>
+        <v>0.5986</v>
       </c>
       <c r="T17" s="6" t="inlineStr"/>
       <c r="U17" s="6" t="inlineStr"/>
@@ -12077,7 +12839,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Juan Martinetti</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -12092,12 +12854,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -12107,23 +12869,23 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -12135,16 +12897,16 @@
         <v>0</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>1.5</v>
+        <v>65.5</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="inlineStr"/>
@@ -12204,7 +12966,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Cody Durden</t>
+          <t>Davey Grant</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -12219,12 +12981,12 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>CODY DURDEN</t>
+          <t>DAVEY GRANT</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>JAFEL FILHO</t>
+          <t>JUAN MARTINETTI</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -12234,23 +12996,23 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 8:40 PM</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -12262,16 +13024,16 @@
         <v>0</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1.5</v>
+        <v>65.5</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T19" s="6" t="inlineStr"/>
       <c r="U19" s="6" t="inlineStr"/>
@@ -12331,7 +13093,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -12346,12 +13108,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -12361,23 +13123,23 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -12389,16 +13151,16 @@
         <v>0</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.5</v>
+        <v>59.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="inlineStr"/>
@@ -12458,7 +13220,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Rafa Garcia</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -12473,12 +13235,12 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -12488,23 +13250,23 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Takedowns</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -12516,16 +13278,16 @@
         <v>0</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>1.5</v>
+        <v>54.5</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>0.5759</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>0.0759</v>
+        <v>0.3271</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.5228</v>
+        <v>0.5981</v>
       </c>
       <c r="T21" s="6" t="inlineStr"/>
       <c r="U21" s="6" t="inlineStr"/>
@@ -12585,7 +13347,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Ryan Spann</t>
+          <t>Youssef Zalal</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -12600,12 +13362,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -12615,7 +13377,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -12631,7 +13393,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -12643,16 +13405,16 @@
         <v>0</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>15.5</v>
+        <v>59.5</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.5599</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.0599</v>
+        <v>0.3271</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.518</v>
+        <v>0.5981</v>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="inlineStr"/>
@@ -12712,7 +13474,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Jackson McVey</t>
+          <t>Aljamain Sterling</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -12727,12 +13489,12 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>JACKSON MCVEY</t>
+          <t>ALJAMAIN STERLING</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>YOUSSEF ZALAL</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -12742,23 +13504,23 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>04/25 6:00 PM</t>
+          <t>04/25 9:40 PM</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -12770,16 +13532,16 @@
         <v>0</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>2.5</v>
+        <v>53.5</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.4989</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>-0.0011</v>
+        <v>0.3271</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.4997</v>
+        <v>0.5981</v>
       </c>
       <c r="T23" s="6" t="inlineStr"/>
       <c r="U23" s="6" t="inlineStr"/>
@@ -12839,7 +13601,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Marcus Buchecha</t>
+          <t>Norma Viana</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -12854,12 +13616,12 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MARCUS BUCHECHA</t>
+          <t>NORMA VIANA</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>RYAN SPANN</t>
+          <t>JOSELYNE EDWARDS</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -12869,23 +13631,23 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:00 PM</t>
+          <t>04/25 9:20 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Total Rounds</t>
+          <t>Significant Strikes</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -12897,16 +13659,16 @@
         <v>0</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>2.5</v>
+        <v>52.5</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.4989</v>
+        <v>0.8161</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>-0.0011</v>
+        <v>0.3161</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.4997</v>
+        <v>0.5948</v>
       </c>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="3" t="inlineStr"/>
@@ -12966,7 +13728,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Raoni Barcelos</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -12981,12 +13743,12 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -12996,23 +13758,23 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -13024,16 +13786,16 @@
         <v>0</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>40.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.4255</v>
+        <v>0.7938</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>-0.0745</v>
+        <v>0.2938</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.4776</v>
+        <v>0.5881</v>
       </c>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
@@ -13093,7 +13855,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Norma Viana</t>
+          <t>Francis Marshall</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -13108,12 +13870,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>NORMA VIANA</t>
+          <t>FRANCIS MARSHALL</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>JOSELYNE EDWARDS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -13123,23 +13885,23 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:20 PM</t>
+          <t>04/25 5:40 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -13151,16 +13913,16 @@
         <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>52.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.417</v>
+        <v>0.7938</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.083</v>
+        <v>0.2938</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.4751</v>
+        <v>0.5881</v>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="3" t="inlineStr"/>
@@ -13220,7 +13982,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Aljamain Sterling</t>
+          <t>Jafel Filho</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -13235,12 +13997,12 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>JAFEL FILHO</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>CODY DURDEN</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -13250,23 +14012,23 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -13278,16 +14040,16 @@
         <v>0</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>53.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.417</v>
+        <v>0.7938</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>-0.083</v>
+        <v>0.2938</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.4751</v>
+        <v>0.5881</v>
       </c>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
@@ -13347,7 +14109,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Montel Jackson</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -13362,12 +14124,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>MONTEL JACKSON</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>RAONI BARCELOS</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -13377,23 +14139,23 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:20 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -13405,16 +14167,16 @@
         <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>38.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.4115</v>
+        <v>0.7938</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>-0.0885</v>
+        <v>0.2938</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.4735</v>
+        <v>0.5881</v>
       </c>
       <c r="T28" s="3" t="inlineStr"/>
       <c r="U28" s="3" t="inlineStr"/>
@@ -13474,7 +14236,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Juan Martinetti</t>
+          <t>Rodolfo Vieira</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -13489,12 +14251,12 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>JUAN MARTINETTI</t>
+          <t>RODOLFO VIEIRA</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>DAVEY GRANT</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -13504,23 +14266,23 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>04/25 8:40 PM</t>
+          <t>04/25 6:20 PM</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -13532,16 +14294,16 @@
         <v>0</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>65.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.7938</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.2938</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5881</v>
       </c>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
@@ -13601,7 +14363,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Davey Grant</t>
+          <t>Alexander Hernandez</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -13616,12 +14378,12 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>DAVEY GRANT</t>
+          <t>ALEXANDER HERNANDEZ</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>JUAN MARTINETTI</t>
+          <t>RAFA GARCIA</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -13631,23 +14393,23 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>04/25 8:40 PM</t>
+          <t>04/25 9:00 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -13659,16 +14421,16 @@
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>65.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.4037</v>
+        <v>0.7938</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-0.0963</v>
+        <v>0.2938</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0.4711</v>
+        <v>0.5881</v>
       </c>
       <c r="T30" s="3" t="inlineStr"/>
       <c r="U30" s="3" t="inlineStr"/>
@@ -13728,7 +14490,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Alexander Hernandez</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -13743,12 +14505,12 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -13758,23 +14520,23 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -13786,16 +14548,16 @@
         <v>0</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>59.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.7689</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.2689</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5807</v>
       </c>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
@@ -13855,7 +14617,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Rafa Garcia</t>
+          <t>Marcus Buchecha</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -13870,12 +14632,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>RAFA GARCIA</t>
+          <t>MARCUS BUCHECHA</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>ALEXANDER HERNANDEZ</t>
+          <t>RYAN SPANN</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -13885,23 +14647,23 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:00 PM</t>
+          <t>04/25 8:00 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
@@ -13913,16 +14675,16 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>54.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>0.4037</v>
+        <v>0.7689</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>-0.0963</v>
+        <v>0.2689</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>0.4711</v>
+        <v>0.5807</v>
       </c>
       <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="3" t="inlineStr"/>
@@ -13982,7 +14744,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Youssef Zalal</t>
+          <t>Jackson McVey</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -13997,12 +14759,12 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>YOUSSEF ZALAL</t>
+          <t>JACKSON MCVEY</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>ALJAMAIN STERLING</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -14012,23 +14774,23 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>04/25 9:40 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr"/>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Total Rounds</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -14040,16 +14802,16 @@
         <v>0</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>59.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0.4037</v>
+        <v>0.6861</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>-0.0963</v>
+        <v>0.1861</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.4711</v>
+        <v>0.5558</v>
       </c>
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
@@ -14109,7 +14871,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Joselyne Edwards</t>
+          <t>Cody Durden</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -14124,12 +14886,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>JOSELYNE EDWARDS</t>
+          <t>CODY DURDEN</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>NORMA VIANA</t>
+          <t>JAFEL FILHO</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -14139,23 +14901,23 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>04/25 9:20 PM</t>
+          <t>04/25 6:00 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Significant Strikes</t>
+          <t>Takedowns</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -14167,16 +14929,16 @@
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>39.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0.3532</v>
+        <v>0.6861</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>-0.1468</v>
+        <v>0.1861</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0.456</v>
+        <v>0.5558</v>
       </c>
       <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="3" t="inlineStr"/>
@@ -14224,6 +14986,387 @@
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Marcus Buchecha</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>MARCUS BUCHECHA</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>RYAN SPANN</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>04/25 8:00 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Total Rounds</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
+      <c r="Y35" s="6" t="inlineStr"/>
+      <c r="Z35" s="6" t="inlineStr"/>
+      <c r="AA35" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB35" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC35" s="6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD35" s="6" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE35" s="6" t="inlineStr"/>
+      <c r="AF35" s="6" t="inlineStr"/>
+      <c r="AG35" s="6" t="inlineStr"/>
+      <c r="AH35" s="6" t="inlineStr"/>
+      <c r="AI35" s="6" t="inlineStr"/>
+      <c r="AJ35" s="6" t="inlineStr"/>
+      <c r="AK35" s="6" t="inlineStr"/>
+      <c r="AL35" s="6" t="inlineStr"/>
+      <c r="AM35" s="6" t="inlineStr"/>
+      <c r="AN35" s="6" t="inlineStr"/>
+      <c r="AO35" s="6" t="inlineStr"/>
+      <c r="AP35" s="6" t="inlineStr"/>
+      <c r="AQ35" s="6" t="inlineStr"/>
+      <c r="AR35" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Marcus Buchecha</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>MARCUS BUCHECHA</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>RYAN SPANN</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>04/25 8:00 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Takedowns</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE36" s="3" t="inlineStr"/>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr"/>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr"/>
+      <c r="AM36" s="3" t="inlineStr"/>
+      <c r="AN36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Youssef Zalal</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>YOUSSEF ZALAL</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>ALJAMAIN STERLING</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>ATP / HARD</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>04/25 9:40 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Takedowns</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="T37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr"/>
+      <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
+      <c r="Y37" s="6" t="inlineStr"/>
+      <c r="Z37" s="6" t="inlineStr"/>
+      <c r="AA37" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB37" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC37" s="6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AD37" s="6" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="AE37" s="6" t="inlineStr"/>
+      <c r="AF37" s="6" t="inlineStr"/>
+      <c r="AG37" s="6" t="inlineStr"/>
+      <c r="AH37" s="6" t="inlineStr"/>
+      <c r="AI37" s="6" t="inlineStr"/>
+      <c r="AJ37" s="6" t="inlineStr"/>
+      <c r="AK37" s="6" t="inlineStr"/>
+      <c r="AL37" s="6" t="inlineStr"/>
+      <c r="AM37" s="6" t="inlineStr"/>
+      <c r="AN37" s="6" t="inlineStr"/>
+      <c r="AO37" s="6" t="inlineStr"/>
+      <c r="AP37" s="6" t="inlineStr"/>
+      <c r="AQ37" s="6" t="inlineStr"/>
+      <c r="AR37" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS37" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AS1"/>
